--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L469"/>
+  <dimension ref="A1:L470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20079,7 +20079,7 @@
         <v>280.72</v>
       </c>
       <c r="C469" t="n">
-        <v>276.37</v>
+        <v>280.58</v>
       </c>
       <c r="D469" t="n">
         <v>277.12</v>
@@ -20108,6 +20108,48 @@
       <c r="L469" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>275.69</v>
+      </c>
+      <c r="C470" t="n">
+        <v>277.3</v>
+      </c>
+      <c r="D470" t="n">
+        <v>273.05</v>
+      </c>
+      <c r="E470" t="n">
+        <v>279.23</v>
+      </c>
+      <c r="F470" t="n">
+        <v>292.08</v>
+      </c>
+      <c r="G470" t="n">
+        <v>305.45</v>
+      </c>
+      <c r="H470" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="I470" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="J470" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="K470" t="n">
+        <v>341.74</v>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20122,7 +20164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B538"/>
+  <dimension ref="A1:B539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25505,6 +25547,16 @@
       </c>
       <c r="B538" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -25673,28 +25725,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3300575202612687</v>
+        <v>-0.3321961030911342</v>
       </c>
       <c r="J2" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K2" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06722769792898142</v>
+        <v>0.06826817134487595</v>
       </c>
       <c r="M2" t="n">
-        <v>7.434345608073436</v>
+        <v>7.427672087125035</v>
       </c>
       <c r="N2" t="n">
-        <v>83.47863383283733</v>
+        <v>83.35868225860405</v>
       </c>
       <c r="O2" t="n">
-        <v>9.136664261799124</v>
+        <v>9.130097604002055</v>
       </c>
       <c r="P2" t="n">
-        <v>289.6419073772249</v>
+        <v>289.6644686254796</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25751,28 +25803,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4101302525022653</v>
+        <v>-0.4083851050300948</v>
       </c>
       <c r="J3" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K3" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08362276668498314</v>
+        <v>0.08327982475231333</v>
       </c>
       <c r="M3" t="n">
-        <v>8.306412897272553</v>
+        <v>8.294247077012797</v>
       </c>
       <c r="N3" t="n">
-        <v>101.8033421827783</v>
+        <v>101.6075281334269</v>
       </c>
       <c r="O3" t="n">
-        <v>10.08976422830476</v>
+        <v>10.08005595884402</v>
       </c>
       <c r="P3" t="n">
-        <v>287.9236629106258</v>
+        <v>287.9054056845558</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25829,28 +25881,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5226568284385315</v>
+        <v>-0.5251457446823118</v>
       </c>
       <c r="J4" t="n">
+        <v>469</v>
+      </c>
+      <c r="K4" t="n">
         <v>468</v>
       </c>
-      <c r="K4" t="n">
-        <v>467</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1123065444321624</v>
+        <v>0.1136196730184904</v>
       </c>
       <c r="M4" t="n">
-        <v>8.590564906698479</v>
+        <v>8.584821068990786</v>
       </c>
       <c r="N4" t="n">
-        <v>119.2138311494172</v>
+        <v>119.039094478912</v>
       </c>
       <c r="O4" t="n">
-        <v>10.91850865042553</v>
+        <v>10.91050385999253</v>
       </c>
       <c r="P4" t="n">
-        <v>292.9318689309049</v>
+        <v>292.9580918508067</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25907,28 +25959,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4909260770822731</v>
+        <v>-0.4947184896806673</v>
       </c>
       <c r="J5" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K5" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1097665292271257</v>
+        <v>0.1115327557216221</v>
       </c>
       <c r="M5" t="n">
-        <v>8.097625861917903</v>
+        <v>8.100101437439255</v>
       </c>
       <c r="N5" t="n">
-        <v>107.9066889672876</v>
+        <v>107.8621423219101</v>
       </c>
       <c r="O5" t="n">
-        <v>10.38781444613291</v>
+        <v>10.38567004684388</v>
       </c>
       <c r="P5" t="n">
-        <v>301.5002347057531</v>
+        <v>301.5401641611588</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25985,28 +26037,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.308486605106959</v>
+        <v>-0.3143526394490196</v>
       </c>
       <c r="J6" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K6" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03751380869453336</v>
+        <v>0.03893487103080251</v>
       </c>
       <c r="M6" t="n">
-        <v>9.10804122903853</v>
+        <v>9.11734577429795</v>
       </c>
       <c r="N6" t="n">
-        <v>134.7901471198939</v>
+        <v>134.9466386263987</v>
       </c>
       <c r="O6" t="n">
-        <v>11.60991589633163</v>
+        <v>11.61665350375911</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6734125896993</v>
+        <v>314.7351747399381</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26063,28 +26115,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05373308162968766</v>
+        <v>0.04130689986170057</v>
       </c>
       <c r="J7" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K7" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0005958365789799913</v>
+        <v>0.0003511003353797726</v>
       </c>
       <c r="M7" t="n">
-        <v>12.69490073891427</v>
+        <v>12.72917419770448</v>
       </c>
       <c r="N7" t="n">
-        <v>265.4288308039851</v>
+        <v>266.8348896532323</v>
       </c>
       <c r="O7" t="n">
-        <v>16.29198670524823</v>
+        <v>16.33508156249097</v>
       </c>
       <c r="P7" t="n">
-        <v>334.4987308208574</v>
+        <v>334.6303568506645</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26141,28 +26193,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2231812067894043</v>
+        <v>0.2108764643972486</v>
       </c>
       <c r="J8" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K8" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007011868204955363</v>
+        <v>0.006260292290830916</v>
       </c>
       <c r="M8" t="n">
-        <v>16.08329129399269</v>
+        <v>16.11185272852966</v>
       </c>
       <c r="N8" t="n">
-        <v>385.1128145875281</v>
+        <v>386.2130849310803</v>
       </c>
       <c r="O8" t="n">
-        <v>19.62429144166811</v>
+        <v>19.65230482490744</v>
       </c>
       <c r="P8" t="n">
-        <v>353.1067344576286</v>
+        <v>353.2374882133485</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26219,28 +26271,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4134252708725771</v>
+        <v>0.4047258206447887</v>
       </c>
       <c r="J9" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01970850014378656</v>
+        <v>0.01894409543329534</v>
       </c>
       <c r="M9" t="n">
-        <v>17.48535357651197</v>
+        <v>17.49144474036702</v>
       </c>
       <c r="N9" t="n">
-        <v>468.4280999359768</v>
+        <v>468.399501856145</v>
       </c>
       <c r="O9" t="n">
-        <v>21.64319985436481</v>
+        <v>21.64253917303016</v>
       </c>
       <c r="P9" t="n">
-        <v>349.7577893804665</v>
+        <v>349.8496156049072</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26297,28 +26349,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5158311987581321</v>
+        <v>0.5191101801879026</v>
       </c>
       <c r="J10" t="n">
+        <v>469</v>
+      </c>
+      <c r="K10" t="n">
         <v>468</v>
       </c>
-      <c r="K10" t="n">
-        <v>467</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02224122658020533</v>
+        <v>0.02260845875764106</v>
       </c>
       <c r="M10" t="n">
-        <v>20.04036245783145</v>
+        <v>20.01255964664295</v>
       </c>
       <c r="N10" t="n">
-        <v>640.9009024024928</v>
+        <v>639.668661129469</v>
       </c>
       <c r="O10" t="n">
-        <v>25.3160206668128</v>
+        <v>25.29167177411309</v>
       </c>
       <c r="P10" t="n">
-        <v>314.6782319838703</v>
+        <v>314.64352319132</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26375,28 +26427,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2277145329164004</v>
+        <v>0.2467624758208861</v>
       </c>
       <c r="J11" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K11" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003031975974064349</v>
+        <v>0.003556119158749316</v>
       </c>
       <c r="M11" t="n">
-        <v>24.60388799740936</v>
+        <v>24.64120026579802</v>
       </c>
       <c r="N11" t="n">
-        <v>939.1875629127372</v>
+        <v>941.8350062675886</v>
       </c>
       <c r="O11" t="n">
-        <v>30.64616718143946</v>
+        <v>30.68933049559062</v>
       </c>
       <c r="P11" t="n">
-        <v>289.012421851103</v>
+        <v>288.8111359981895</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -26438,7 +26490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L469"/>
+  <dimension ref="A1:L470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55394,7 +55446,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>-45.90701910468701,170.5627035273566</t>
+          <t>-45.90705636558217,170.56271326112523</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -55440,6 +55492,68 @@
       <c r="L469" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-45.90688824872749,170.5635821709082</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-45.907027335716165,170.5627056775705</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-45.90711455806493,170.5618156358213</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-45.90729409168291,170.56094970769186</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-45.90752987902192,170.56012111601407</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-45.90772511561554,170.55928976194878</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-45.90796650242236,170.55841806756217</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-45.908090300610795,170.55752468697796</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-45.90807445454714,170.5566352903754</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>-45.90796448990179,170.555751660184</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L470"/>
+  <dimension ref="A1:L471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20079,7 +20079,7 @@
         <v>280.72</v>
       </c>
       <c r="C469" t="n">
-        <v>280.58</v>
+        <v>276.37</v>
       </c>
       <c r="D469" t="n">
         <v>277.12</v>
@@ -20121,7 +20121,7 @@
         <v>275.69</v>
       </c>
       <c r="C470" t="n">
-        <v>277.3</v>
+        <v>270.39</v>
       </c>
       <c r="D470" t="n">
         <v>273.05</v>
@@ -20133,10 +20133,10 @@
         <v>292.08</v>
       </c>
       <c r="G470" t="n">
-        <v>305.45</v>
+        <v>313.4</v>
       </c>
       <c r="H470" t="n">
-        <v>328.92</v>
+        <v>333.48</v>
       </c>
       <c r="I470" t="n">
         <v>339.23</v>
@@ -20145,9 +20145,51 @@
         <v>336.29</v>
       </c>
       <c r="K470" t="n">
-        <v>341.74</v>
+        <v>342.17</v>
       </c>
       <c r="L470" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>274.69</v>
+      </c>
+      <c r="C471" t="n">
+        <v>268.91</v>
+      </c>
+      <c r="D471" t="n">
+        <v>272.6</v>
+      </c>
+      <c r="E471" t="n">
+        <v>287.29</v>
+      </c>
+      <c r="F471" t="n">
+        <v>308.35</v>
+      </c>
+      <c r="G471" t="n">
+        <v>334.46</v>
+      </c>
+      <c r="H471" t="n">
+        <v>348.99</v>
+      </c>
+      <c r="I471" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="J471" t="n">
+        <v>340.62</v>
+      </c>
+      <c r="K471" t="n">
+        <v>340.6</v>
+      </c>
+      <c r="L471" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20164,7 +20206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B539"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25557,6 +25599,16 @@
       </c>
       <c r="B539" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -25725,28 +25777,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3321961030911342</v>
+        <v>-0.3347171692662511</v>
       </c>
       <c r="J2" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K2" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06826817134487595</v>
+        <v>0.06944892990090135</v>
       </c>
       <c r="M2" t="n">
-        <v>7.427672087125035</v>
+        <v>7.422702640194834</v>
       </c>
       <c r="N2" t="n">
-        <v>83.35868225860405</v>
+        <v>83.26232894821331</v>
       </c>
       <c r="O2" t="n">
-        <v>9.130097604002055</v>
+        <v>9.124819392635304</v>
       </c>
       <c r="P2" t="n">
-        <v>289.6644686254796</v>
+        <v>289.6911446198416</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25803,28 +25855,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4083851050300948</v>
+        <v>-0.4161759119816952</v>
       </c>
       <c r="J3" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K3" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08327982475231333</v>
+        <v>0.08638120255994719</v>
       </c>
       <c r="M3" t="n">
-        <v>8.294247077012797</v>
+        <v>8.302242363654907</v>
       </c>
       <c r="N3" t="n">
-        <v>101.6075281334269</v>
+        <v>101.6055849309443</v>
       </c>
       <c r="O3" t="n">
-        <v>10.08005595884402</v>
+        <v>10.07995956990624</v>
       </c>
       <c r="P3" t="n">
-        <v>287.9054056845558</v>
+        <v>287.9875469556289</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25881,28 +25933,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5251457446823118</v>
+        <v>-0.527786337138849</v>
       </c>
       <c r="J4" t="n">
+        <v>470</v>
+      </c>
+      <c r="K4" t="n">
         <v>469</v>
       </c>
-      <c r="K4" t="n">
-        <v>468</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1136196730184904</v>
+        <v>0.1149929666746889</v>
       </c>
       <c r="M4" t="n">
-        <v>8.584821068990786</v>
+        <v>8.579785540327554</v>
       </c>
       <c r="N4" t="n">
-        <v>119.039094478912</v>
+        <v>118.8752074890969</v>
       </c>
       <c r="O4" t="n">
-        <v>10.91050385999253</v>
+        <v>10.90299075892009</v>
       </c>
       <c r="P4" t="n">
-        <v>292.9580918508067</v>
+        <v>292.9859957701299</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25959,28 +26011,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4947184896806673</v>
+        <v>-0.4952082433101345</v>
       </c>
       <c r="J5" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K5" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1115327557216221</v>
+        <v>0.1121530274110923</v>
       </c>
       <c r="M5" t="n">
-        <v>8.100101437439255</v>
+        <v>8.085455746290693</v>
       </c>
       <c r="N5" t="n">
-        <v>107.8621423219101</v>
+        <v>107.6357387429248</v>
       </c>
       <c r="O5" t="n">
-        <v>10.38567004684388</v>
+        <v>10.37476451505888</v>
       </c>
       <c r="P5" t="n">
-        <v>301.5401641611588</v>
+        <v>301.5453360058529</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26037,28 +26089,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3143526394490196</v>
+        <v>-0.3135794606165962</v>
       </c>
       <c r="J6" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K6" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03893487103080251</v>
+        <v>0.03890912151425041</v>
       </c>
       <c r="M6" t="n">
-        <v>9.11734577429795</v>
+        <v>9.102239321808442</v>
       </c>
       <c r="N6" t="n">
-        <v>134.9466386263987</v>
+        <v>134.6672202508647</v>
       </c>
       <c r="O6" t="n">
-        <v>11.61665350375911</v>
+        <v>11.60462064226422</v>
       </c>
       <c r="P6" t="n">
-        <v>314.7351747399381</v>
+        <v>314.7270098982679</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26115,28 +26167,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04130689986170057</v>
+        <v>0.04401363722282463</v>
       </c>
       <c r="J7" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K7" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003511003353797726</v>
+        <v>0.0004016623363716221</v>
       </c>
       <c r="M7" t="n">
-        <v>12.72917419770448</v>
+        <v>12.68859883989174</v>
       </c>
       <c r="N7" t="n">
-        <v>266.8348896532323</v>
+        <v>265.3744043341134</v>
       </c>
       <c r="O7" t="n">
-        <v>16.33508156249097</v>
+        <v>16.29031627483375</v>
       </c>
       <c r="P7" t="n">
-        <v>334.6303568506645</v>
+        <v>334.6017021798191</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26193,28 +26245,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2108764643972486</v>
+        <v>0.2087174092305026</v>
       </c>
       <c r="J8" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K8" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006260292290830916</v>
+        <v>0.006165132733307988</v>
       </c>
       <c r="M8" t="n">
-        <v>16.11185272852966</v>
+        <v>16.08826891160799</v>
       </c>
       <c r="N8" t="n">
-        <v>386.2130849310803</v>
+        <v>385.0530910936087</v>
       </c>
       <c r="O8" t="n">
-        <v>19.65230482490744</v>
+        <v>19.6227697100488</v>
       </c>
       <c r="P8" t="n">
-        <v>353.2374882133485</v>
+        <v>353.2605575119654</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26271,28 +26323,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4047258206447887</v>
+        <v>0.3991499634175643</v>
       </c>
       <c r="J9" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K9" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01894409543329534</v>
+        <v>0.01849759649662908</v>
       </c>
       <c r="M9" t="n">
-        <v>17.49144474036702</v>
+        <v>17.48176266873405</v>
       </c>
       <c r="N9" t="n">
-        <v>468.399501856145</v>
+        <v>467.7984599030383</v>
       </c>
       <c r="O9" t="n">
-        <v>21.64253917303016</v>
+        <v>21.62864905404492</v>
       </c>
       <c r="P9" t="n">
-        <v>349.8496156049072</v>
+        <v>349.9086464373847</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26349,28 +26401,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5191101801879026</v>
+        <v>0.5241211648344836</v>
       </c>
       <c r="J10" t="n">
+        <v>470</v>
+      </c>
+      <c r="K10" t="n">
         <v>469</v>
       </c>
-      <c r="K10" t="n">
-        <v>468</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02260845875764106</v>
+        <v>0.0231227767261788</v>
       </c>
       <c r="M10" t="n">
-        <v>20.01255964664295</v>
+        <v>19.992661755119</v>
       </c>
       <c r="N10" t="n">
-        <v>639.668661129469</v>
+        <v>638.6247992031657</v>
       </c>
       <c r="O10" t="n">
-        <v>25.29167177411309</v>
+        <v>25.27102687274828</v>
       </c>
       <c r="P10" t="n">
-        <v>314.64352319132</v>
+        <v>314.5903239665062</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26427,28 +26479,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2467624758208861</v>
+        <v>0.2653859035260298</v>
       </c>
       <c r="J11" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K11" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003556119158749316</v>
+        <v>0.004109067673821243</v>
       </c>
       <c r="M11" t="n">
-        <v>24.64120026579802</v>
+        <v>24.67599256043145</v>
       </c>
       <c r="N11" t="n">
-        <v>941.8350062675886</v>
+        <v>944.2723873980501</v>
       </c>
       <c r="O11" t="n">
-        <v>30.68933049559062</v>
+        <v>30.72901539909878</v>
       </c>
       <c r="P11" t="n">
-        <v>288.8111359981895</v>
+        <v>288.6137537690946</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -26490,7 +26542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L470"/>
+  <dimension ref="A1:L471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55446,7 +55498,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>-45.90705636558217,170.56271326112523</t>
+          <t>-45.90701910468701,170.5627035273566</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -55508,7 +55560,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>-45.907027335716165,170.5627056775705</t>
+          <t>-45.906966178283476,170.56268970126416</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -55528,12 +55580,12 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>-45.90772511561554,170.55928976194878</t>
+          <t>-45.90779647365738,170.5592967032653</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>-45.90796650242236,170.55841806756217</t>
+          <t>-45.90800750921165,170.55841977660725</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -55548,10 +55600,72 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>-45.90796448990179,170.555751660184</t>
+          <t>-45.90796821380863,170.55575015926394</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-45.9068793981677,170.5635798587594</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-45.90695307944089,170.56268627942563</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-45.90711057530462,170.56181459543782</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-45.907365427416465,170.56096834143148</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-45.9076747470483,170.5601511114581</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-45.9079855051451,170.55931509127348</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>-45.90814698624973,170.55842558961874</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-45.90815839800528,170.5575260091599</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>-45.90811303670143,170.556627589084</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>-45.90795461721842,170.55575563936648</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L471"/>
+  <dimension ref="A1:L472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20190,6 +20190,48 @@
         <v>340.6</v>
       </c>
       <c r="L471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>276.28</v>
+      </c>
+      <c r="C472" t="n">
+        <v>270.91</v>
+      </c>
+      <c r="D472" t="n">
+        <v>276.58</v>
+      </c>
+      <c r="E472" t="n">
+        <v>291.77</v>
+      </c>
+      <c r="F472" t="n">
+        <v>314.39</v>
+      </c>
+      <c r="G472" t="n">
+        <v>344.63</v>
+      </c>
+      <c r="H472" t="n">
+        <v>360.92</v>
+      </c>
+      <c r="I472" t="n">
+        <v>356.73</v>
+      </c>
+      <c r="J472" t="n">
+        <v>342.28</v>
+      </c>
+      <c r="K472" t="n">
+        <v>335.86</v>
+      </c>
+      <c r="L472" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20206,7 +20248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25609,6 +25651,16 @@
       </c>
       <c r="B540" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -25777,28 +25829,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3347171692662511</v>
+        <v>-0.3365708115404419</v>
       </c>
       <c r="J2" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K2" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06944892990090135</v>
+        <v>0.07041352726773709</v>
       </c>
       <c r="M2" t="n">
-        <v>7.422702640194834</v>
+        <v>7.414800577571024</v>
       </c>
       <c r="N2" t="n">
-        <v>83.26232894821331</v>
+        <v>83.128566764117</v>
       </c>
       <c r="O2" t="n">
-        <v>9.124819392635304</v>
+        <v>9.117486866681904</v>
       </c>
       <c r="P2" t="n">
-        <v>289.6911446198416</v>
+        <v>289.7108393262326</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25855,28 +25907,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4161759119816952</v>
+        <v>-0.4186428236211772</v>
       </c>
       <c r="J3" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K3" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08638120255994719</v>
+        <v>0.08760161022686497</v>
       </c>
       <c r="M3" t="n">
-        <v>8.302242363654907</v>
+        <v>8.297144870157487</v>
       </c>
       <c r="N3" t="n">
-        <v>101.6055849309443</v>
+        <v>101.4666730823196</v>
       </c>
       <c r="O3" t="n">
-        <v>10.07995956990624</v>
+        <v>10.07306671686034</v>
       </c>
       <c r="P3" t="n">
-        <v>287.9875469556289</v>
+        <v>288.0137575687062</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25933,28 +25985,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.527786337138849</v>
+        <v>-0.5287794272385395</v>
       </c>
       <c r="J4" t="n">
+        <v>471</v>
+      </c>
+      <c r="K4" t="n">
         <v>470</v>
       </c>
-      <c r="K4" t="n">
-        <v>469</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1149929666746889</v>
+        <v>0.1158073482762747</v>
       </c>
       <c r="M4" t="n">
-        <v>8.579785540327554</v>
+        <v>8.566485155701731</v>
       </c>
       <c r="N4" t="n">
-        <v>118.8752074890969</v>
+        <v>118.6349273186215</v>
       </c>
       <c r="O4" t="n">
-        <v>10.90299075892009</v>
+        <v>10.8919661824035</v>
       </c>
       <c r="P4" t="n">
-        <v>292.9859957701299</v>
+        <v>292.9965331148434</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26011,28 +26063,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4952082433101345</v>
+        <v>-0.4938586085807968</v>
       </c>
       <c r="J5" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K5" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1121530274110923</v>
+        <v>0.1120189684036502</v>
       </c>
       <c r="M5" t="n">
-        <v>8.085455746290693</v>
+        <v>8.075315899720531</v>
       </c>
       <c r="N5" t="n">
-        <v>107.6357387429248</v>
+        <v>107.4305459277959</v>
       </c>
       <c r="O5" t="n">
-        <v>10.37476451505888</v>
+        <v>10.36487076271557</v>
       </c>
       <c r="P5" t="n">
-        <v>301.5453360058529</v>
+        <v>301.5310253806556</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26089,28 +26141,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3135794606165962</v>
+        <v>-0.3103496570698112</v>
       </c>
       <c r="J6" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K6" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03890912151425041</v>
+        <v>0.03826467472794004</v>
       </c>
       <c r="M6" t="n">
-        <v>9.102239321808442</v>
+        <v>9.10073342817792</v>
       </c>
       <c r="N6" t="n">
-        <v>134.6672202508647</v>
+        <v>134.5149293521843</v>
       </c>
       <c r="O6" t="n">
-        <v>11.60462064226422</v>
+        <v>11.59805713695981</v>
       </c>
       <c r="P6" t="n">
-        <v>314.7270098982679</v>
+        <v>314.6927632187671</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26167,28 +26219,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04401363722282463</v>
+        <v>0.04763484875477847</v>
       </c>
       <c r="J7" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K7" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004016623363716221</v>
+        <v>0.0004721886219204441</v>
       </c>
       <c r="M7" t="n">
-        <v>12.68859883989174</v>
+        <v>12.68155887182595</v>
       </c>
       <c r="N7" t="n">
-        <v>265.3744043341134</v>
+        <v>264.9750637547102</v>
       </c>
       <c r="O7" t="n">
-        <v>16.29031627483375</v>
+        <v>16.27805466739531</v>
       </c>
       <c r="P7" t="n">
-        <v>334.6017021798191</v>
+        <v>334.5630732962824</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26245,28 +26297,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2087174092305026</v>
+        <v>0.2095941666874853</v>
       </c>
       <c r="J8" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K8" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006165132733307988</v>
+        <v>0.0062434276535005</v>
       </c>
       <c r="M8" t="n">
-        <v>16.08826891160799</v>
+        <v>16.05856432621302</v>
       </c>
       <c r="N8" t="n">
-        <v>385.0530910936087</v>
+        <v>384.2400403210536</v>
       </c>
       <c r="O8" t="n">
-        <v>19.6227697100488</v>
+        <v>19.60204173858054</v>
       </c>
       <c r="P8" t="n">
-        <v>353.2605575119654</v>
+        <v>353.2511752138402</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26323,28 +26375,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3991499634175643</v>
+        <v>0.3976275888993989</v>
       </c>
       <c r="J9" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K9" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01849759649662908</v>
+        <v>0.01843637030789913</v>
       </c>
       <c r="M9" t="n">
-        <v>17.48176266873405</v>
+        <v>17.4519624822349</v>
       </c>
       <c r="N9" t="n">
-        <v>467.7984599030383</v>
+        <v>466.8306528525059</v>
       </c>
       <c r="O9" t="n">
-        <v>21.62864905404492</v>
+        <v>21.60626420398737</v>
       </c>
       <c r="P9" t="n">
-        <v>349.9086464373847</v>
+        <v>349.9248297140886</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26401,28 +26453,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5241211648344836</v>
+        <v>0.5297657377729925</v>
       </c>
       <c r="J10" t="n">
+        <v>471</v>
+      </c>
+      <c r="K10" t="n">
         <v>470</v>
       </c>
-      <c r="K10" t="n">
-        <v>469</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0231227767261788</v>
+        <v>0.02369734990365358</v>
       </c>
       <c r="M10" t="n">
-        <v>19.992661755119</v>
+        <v>19.9755205577498</v>
       </c>
       <c r="N10" t="n">
-        <v>638.6247992031657</v>
+        <v>637.6697595274866</v>
       </c>
       <c r="O10" t="n">
-        <v>25.27102687274828</v>
+        <v>25.25212386171679</v>
       </c>
       <c r="P10" t="n">
-        <v>314.5903239665062</v>
+        <v>314.5301544645713</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26479,28 +26531,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2653859035260298</v>
+        <v>0.2818010236306514</v>
       </c>
       <c r="J11" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K11" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004109067673821243</v>
+        <v>0.004633844504683293</v>
       </c>
       <c r="M11" t="n">
-        <v>24.67599256043145</v>
+        <v>24.70151386980239</v>
       </c>
       <c r="N11" t="n">
-        <v>944.2723873980501</v>
+        <v>945.6919905934702</v>
       </c>
       <c r="O11" t="n">
-        <v>30.72901539909878</v>
+        <v>30.75210546602412</v>
       </c>
       <c r="P11" t="n">
-        <v>288.6137537690946</v>
+        <v>288.4390561775399</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -26542,7 +26594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L471"/>
+  <dimension ref="A1:L472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55671,6 +55723,68 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-45.90689347055773,170.56358353507628</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-45.906970780579485,170.56269090353211</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-45.90714580060661,170.5618237970563</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-45.90740507804626,170.56097869866562</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-45.90772852718633,170.56016224686473</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>-45.90807678957927,170.55932397098798</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-45.90825426935963,170.55843006088782</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>-45.908247725233714,170.5575277435409</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>-45.908127828012056,170.55662463662273</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>-45.907913567638204,170.5557721843725</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L472"/>
+  <dimension ref="A1:L473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20234,6 +20234,48 @@
       <c r="L472" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>286.12</v>
+      </c>
+      <c r="C473" t="n">
+        <v>294.84</v>
+      </c>
+      <c r="D473" t="n">
+        <v>293.65</v>
+      </c>
+      <c r="E473" t="n">
+        <v>306.01</v>
+      </c>
+      <c r="F473" t="n">
+        <v>328.94</v>
+      </c>
+      <c r="G473" t="n">
+        <v>360.1</v>
+      </c>
+      <c r="H473" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="I473" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="J473" t="n">
+        <v>348.87</v>
+      </c>
+      <c r="K473" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20248,7 +20290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25661,6 +25703,16 @@
       </c>
       <c r="B541" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>-0.93</v>
       </c>
     </row>
   </sheetData>
@@ -25829,28 +25881,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3365708115404419</v>
+        <v>-0.3343867133785514</v>
       </c>
       <c r="J2" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K2" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07041352726773709</v>
+        <v>0.06980180095328492</v>
       </c>
       <c r="M2" t="n">
-        <v>7.414800577571024</v>
+        <v>7.412418889804602</v>
       </c>
       <c r="N2" t="n">
-        <v>83.128566764117</v>
+        <v>83.01201673633099</v>
       </c>
       <c r="O2" t="n">
-        <v>9.117486866681904</v>
+        <v>9.111093059360716</v>
       </c>
       <c r="P2" t="n">
-        <v>289.7108393262326</v>
+        <v>289.6875158823923</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25907,28 +25959,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4186428236211772</v>
+        <v>-0.411319646224685</v>
       </c>
       <c r="J3" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K3" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08760161022686497</v>
+        <v>0.08463924353778218</v>
       </c>
       <c r="M3" t="n">
-        <v>8.297144870157487</v>
+        <v>8.318440981762162</v>
       </c>
       <c r="N3" t="n">
-        <v>101.4666730823196</v>
+        <v>101.9326926027324</v>
       </c>
       <c r="O3" t="n">
-        <v>10.07306671686034</v>
+        <v>10.09617217576703</v>
       </c>
       <c r="P3" t="n">
-        <v>288.0137575687062</v>
+        <v>287.9355551693268</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25985,28 +26037,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5287794272385395</v>
+        <v>-0.5227858206710173</v>
       </c>
       <c r="J4" t="n">
+        <v>472</v>
+      </c>
+      <c r="K4" t="n">
         <v>471</v>
       </c>
-      <c r="K4" t="n">
-        <v>470</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1158073482762747</v>
+        <v>0.1135465839282047</v>
       </c>
       <c r="M4" t="n">
-        <v>8.566485155701731</v>
+        <v>8.580908967474357</v>
       </c>
       <c r="N4" t="n">
-        <v>118.6349273186215</v>
+        <v>118.8392176479169</v>
       </c>
       <c r="O4" t="n">
-        <v>10.8919661824035</v>
+        <v>10.90134017669006</v>
       </c>
       <c r="P4" t="n">
-        <v>292.9965331148434</v>
+        <v>292.9326159638102</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26063,28 +26115,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4938586085807968</v>
+        <v>-0.4866901590098518</v>
       </c>
       <c r="J5" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K5" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1120189684036502</v>
+        <v>0.1089795009683707</v>
       </c>
       <c r="M5" t="n">
-        <v>8.075315899720531</v>
+        <v>8.095915407218284</v>
       </c>
       <c r="N5" t="n">
-        <v>107.4305459277959</v>
+        <v>107.8548468785086</v>
       </c>
       <c r="O5" t="n">
-        <v>10.36487076271557</v>
+        <v>10.3853188144856</v>
       </c>
       <c r="P5" t="n">
-        <v>301.5310253806556</v>
+        <v>301.4546331466104</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26141,28 +26193,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3103496570698112</v>
+        <v>-0.3011859776773002</v>
       </c>
       <c r="J6" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K6" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03826467472794004</v>
+        <v>0.03599625561913089</v>
       </c>
       <c r="M6" t="n">
-        <v>9.10073342817792</v>
+        <v>9.131828369421605</v>
       </c>
       <c r="N6" t="n">
-        <v>134.5149293521843</v>
+        <v>135.295249204353</v>
       </c>
       <c r="O6" t="n">
-        <v>11.59805713695981</v>
+        <v>11.63164860216956</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6927632187671</v>
+        <v>314.5951083585438</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26219,28 +26271,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04763484875477847</v>
+        <v>0.05758482793489945</v>
       </c>
       <c r="J7" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K7" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004721886219204441</v>
+        <v>0.0006896893515392355</v>
       </c>
       <c r="M7" t="n">
-        <v>12.68155887182595</v>
+        <v>12.7090249745431</v>
       </c>
       <c r="N7" t="n">
-        <v>264.9750637547102</v>
+        <v>265.6560462913966</v>
       </c>
       <c r="O7" t="n">
-        <v>16.27805466739531</v>
+        <v>16.29895844191882</v>
       </c>
       <c r="P7" t="n">
-        <v>334.5630732962824</v>
+        <v>334.4564002996745</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26297,28 +26349,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2095941666874853</v>
+        <v>0.2147667709338915</v>
       </c>
       <c r="J8" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K8" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0062434276535005</v>
+        <v>0.006576305751048839</v>
       </c>
       <c r="M8" t="n">
-        <v>16.05856432621302</v>
+        <v>16.05155382323564</v>
       </c>
       <c r="N8" t="n">
-        <v>384.2400403210536</v>
+        <v>383.7555176869658</v>
       </c>
       <c r="O8" t="n">
-        <v>19.60204173858054</v>
+        <v>19.58967885614682</v>
       </c>
       <c r="P8" t="n">
-        <v>353.2511752138402</v>
+        <v>353.1955452633394</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26375,28 +26427,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3976275888993989</v>
+        <v>0.3987244994108964</v>
       </c>
       <c r="J9" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K9" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01843637030789913</v>
+        <v>0.01861560354738268</v>
       </c>
       <c r="M9" t="n">
-        <v>17.4519624822349</v>
+        <v>17.42086868907167</v>
       </c>
       <c r="N9" t="n">
-        <v>466.8306528525059</v>
+        <v>465.8526302518201</v>
       </c>
       <c r="O9" t="n">
-        <v>21.60626420398737</v>
+        <v>21.5836194891362</v>
       </c>
       <c r="P9" t="n">
-        <v>349.9248297140886</v>
+        <v>349.9131104186422</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26453,28 +26505,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5297657377729925</v>
+        <v>0.5380762560483286</v>
       </c>
       <c r="J10" t="n">
+        <v>472</v>
+      </c>
+      <c r="K10" t="n">
         <v>471</v>
       </c>
-      <c r="K10" t="n">
-        <v>470</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02369734990365358</v>
+        <v>0.02450077070358969</v>
       </c>
       <c r="M10" t="n">
-        <v>19.9755205577498</v>
+        <v>19.97006838031681</v>
       </c>
       <c r="N10" t="n">
-        <v>637.6697595274866</v>
+        <v>637.1826043516982</v>
       </c>
       <c r="O10" t="n">
-        <v>25.25212386171679</v>
+        <v>25.242476192951</v>
       </c>
       <c r="P10" t="n">
-        <v>314.5301544645713</v>
+        <v>314.4411235275114</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26531,28 +26583,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2818010236306514</v>
+        <v>0.3001763134898995</v>
       </c>
       <c r="J11" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K11" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004633844504683293</v>
+        <v>0.005253892873256394</v>
       </c>
       <c r="M11" t="n">
-        <v>24.70151386980239</v>
+        <v>24.73538007766489</v>
       </c>
       <c r="N11" t="n">
-        <v>945.6919905934702</v>
+        <v>947.9419955942947</v>
       </c>
       <c r="O11" t="n">
-        <v>30.75210546602412</v>
+        <v>30.78866667451344</v>
       </c>
       <c r="P11" t="n">
-        <v>288.4390561775399</v>
+        <v>288.2425085773903</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -26594,7 +26646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L472"/>
+  <dimension ref="A1:L473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55785,6 +55837,68 @@
         </is>
       </c>
     </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-45.906980560063346,170.5636062866606</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-45.907182574689166,170.56274623117682</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-45.90729687997167,170.56186326241144</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-45.90753111039934,170.56101161996475</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-45.90785808032882,170.5601890714754</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-45.90821564603635,170.55933747832637</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-45.908348423101806,170.55843398496765</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-45.90830565749401,170.5575288683558</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>-45.90818654773173,170.5566129156902</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>-45.90795617606317,170.5557550110746</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L473"/>
+  <dimension ref="A1:L475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20276,6 +20276,90 @@
       <c r="L473" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>286.04</v>
+      </c>
+      <c r="C474" t="n">
+        <v>292.46</v>
+      </c>
+      <c r="D474" t="n">
+        <v>292.46</v>
+      </c>
+      <c r="E474" t="n">
+        <v>303.92</v>
+      </c>
+      <c r="F474" t="n">
+        <v>325.36</v>
+      </c>
+      <c r="G474" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="H474" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="I474" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="J474" t="n">
+        <v>348.87</v>
+      </c>
+      <c r="K474" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>290.83</v>
+      </c>
+      <c r="C475" t="n">
+        <v>289.14</v>
+      </c>
+      <c r="D475" t="n">
+        <v>290.66</v>
+      </c>
+      <c r="E475" t="n">
+        <v>299.96</v>
+      </c>
+      <c r="F475" t="n">
+        <v>323.89</v>
+      </c>
+      <c r="G475" t="n">
+        <v>358.9</v>
+      </c>
+      <c r="H475" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="I475" t="n">
+        <v>376.8</v>
+      </c>
+      <c r="J475" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="K475" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25713,6 +25797,26 @@
       </c>
       <c r="B542" t="n">
         <v>-0.93</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -25881,28 +25985,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3343867133785514</v>
+        <v>-0.3281899249959167</v>
       </c>
       <c r="J2" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K2" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06980180095328492</v>
+        <v>0.06775524627481266</v>
       </c>
       <c r="M2" t="n">
-        <v>7.412418889804602</v>
+        <v>7.418860958959292</v>
       </c>
       <c r="N2" t="n">
-        <v>83.01201673633099</v>
+        <v>82.92931276399923</v>
       </c>
       <c r="O2" t="n">
-        <v>9.111093059360716</v>
+        <v>9.106553286727049</v>
       </c>
       <c r="P2" t="n">
-        <v>289.6875158823923</v>
+        <v>289.6211659898114</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25959,28 +26063,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.411319646224685</v>
+        <v>-0.4001341959695069</v>
       </c>
       <c r="J3" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K3" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08463924353778218</v>
+        <v>0.08051919329369484</v>
       </c>
       <c r="M3" t="n">
-        <v>8.318440981762162</v>
+        <v>8.342139366223661</v>
       </c>
       <c r="N3" t="n">
-        <v>101.9326926027324</v>
+        <v>102.3116637296743</v>
       </c>
       <c r="O3" t="n">
-        <v>10.09617217576703</v>
+        <v>10.1149228237132</v>
       </c>
       <c r="P3" t="n">
-        <v>287.9355551693268</v>
+        <v>287.8158170613873</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26037,28 +26141,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5227858206710173</v>
+        <v>-0.5126413273849807</v>
       </c>
       <c r="J4" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K4" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1135465839282047</v>
+        <v>0.1099707315297406</v>
       </c>
       <c r="M4" t="n">
-        <v>8.580908967474357</v>
+        <v>8.599994590402783</v>
       </c>
       <c r="N4" t="n">
-        <v>118.8392176479169</v>
+        <v>118.9969049908</v>
       </c>
       <c r="O4" t="n">
-        <v>10.90134017669006</v>
+        <v>10.90857025419922</v>
       </c>
       <c r="P4" t="n">
-        <v>292.9326159638102</v>
+        <v>292.8241674523326</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26115,28 +26219,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4866901590098518</v>
+        <v>-0.4758262007235368</v>
       </c>
       <c r="J5" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K5" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1089795009683707</v>
+        <v>0.1048222737963092</v>
       </c>
       <c r="M5" t="n">
-        <v>8.095915407218284</v>
+        <v>8.119181226469134</v>
       </c>
       <c r="N5" t="n">
-        <v>107.8548468785086</v>
+        <v>108.1688235260911</v>
       </c>
       <c r="O5" t="n">
-        <v>10.3853188144856</v>
+        <v>10.40042419933394</v>
       </c>
       <c r="P5" t="n">
-        <v>301.4546331466104</v>
+        <v>301.3385798730137</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26193,28 +26297,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3011859776773002</v>
+        <v>-0.2865990811456606</v>
       </c>
       <c r="J6" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K6" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03599625561913089</v>
+        <v>0.03266418620646483</v>
       </c>
       <c r="M6" t="n">
-        <v>9.131828369421605</v>
+        <v>9.173492743984104</v>
       </c>
       <c r="N6" t="n">
-        <v>135.295249204353</v>
+        <v>136.0832654824488</v>
       </c>
       <c r="O6" t="n">
-        <v>11.63164860216956</v>
+        <v>11.66547322153923</v>
       </c>
       <c r="P6" t="n">
-        <v>314.5951083585438</v>
+        <v>314.4392768770994</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26271,28 +26375,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05758482793489945</v>
+        <v>0.07527870824388562</v>
       </c>
       <c r="J7" t="n">
+        <v>474</v>
+      </c>
+      <c r="K7" t="n">
         <v>472</v>
       </c>
-      <c r="K7" t="n">
-        <v>470</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0006896893515392355</v>
+        <v>0.001179574511618209</v>
       </c>
       <c r="M7" t="n">
-        <v>12.7090249745431</v>
+        <v>12.75303012857044</v>
       </c>
       <c r="N7" t="n">
-        <v>265.6560462913966</v>
+        <v>266.5139776220969</v>
       </c>
       <c r="O7" t="n">
-        <v>16.29895844191882</v>
+        <v>16.32525582103071</v>
       </c>
       <c r="P7" t="n">
-        <v>334.4564002996745</v>
+        <v>334.2662310214204</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26349,28 +26453,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2147667709338915</v>
+        <v>0.2298257761348697</v>
       </c>
       <c r="J8" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K8" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006576305751048839</v>
+        <v>0.007560029992639272</v>
       </c>
       <c r="M8" t="n">
-        <v>16.05155382323564</v>
+        <v>16.0619176882555</v>
       </c>
       <c r="N8" t="n">
-        <v>383.7555176869658</v>
+        <v>383.6216157362432</v>
       </c>
       <c r="O8" t="n">
-        <v>19.58967885614682</v>
+        <v>19.58626089217243</v>
       </c>
       <c r="P8" t="n">
-        <v>353.1955452633394</v>
+        <v>353.0331719987889</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26427,28 +26531,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3987244994108964</v>
+        <v>0.4063975197933926</v>
       </c>
       <c r="J9" t="n">
+        <v>474</v>
+      </c>
+      <c r="K9" t="n">
         <v>472</v>
       </c>
-      <c r="K9" t="n">
-        <v>470</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01861560354738268</v>
+        <v>0.01946780251844793</v>
       </c>
       <c r="M9" t="n">
-        <v>17.42086868907167</v>
+        <v>17.38889264427404</v>
       </c>
       <c r="N9" t="n">
-        <v>465.8526302518201</v>
+        <v>464.4490394111053</v>
       </c>
       <c r="O9" t="n">
-        <v>21.5836194891362</v>
+        <v>21.5510797736704</v>
       </c>
       <c r="P9" t="n">
-        <v>349.9131104186422</v>
+        <v>349.8308990639987</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26505,28 +26609,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5380762560483286</v>
+        <v>0.5574291563332879</v>
       </c>
       <c r="J10" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K10" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02450077070358969</v>
+        <v>0.02637493101740984</v>
       </c>
       <c r="M10" t="n">
-        <v>19.97006838031681</v>
+        <v>19.9729290542022</v>
       </c>
       <c r="N10" t="n">
-        <v>637.1826043516982</v>
+        <v>636.9065507220449</v>
       </c>
       <c r="O10" t="n">
-        <v>25.242476192951</v>
+        <v>25.23700756274493</v>
       </c>
       <c r="P10" t="n">
-        <v>314.4411235275114</v>
+        <v>314.2332676538847</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26583,28 +26687,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3001763134898995</v>
+        <v>0.3392654604373088</v>
       </c>
       <c r="J11" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K11" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005253892873256394</v>
+        <v>0.00669125736496512</v>
       </c>
       <c r="M11" t="n">
-        <v>24.73538007766489</v>
+        <v>24.81311986280667</v>
       </c>
       <c r="N11" t="n">
-        <v>947.9419955942947</v>
+        <v>953.6714389476291</v>
       </c>
       <c r="O11" t="n">
-        <v>30.78866667451344</v>
+        <v>30.88157118651234</v>
       </c>
       <c r="P11" t="n">
-        <v>288.2425085773903</v>
+        <v>287.8233413892212</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -26646,7 +26750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L473"/>
+  <dimension ref="A1:L475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55899,6 +56003,130 @@
         </is>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-45.90697985201861,170.5636061016881</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-45.90716151033674,170.56274072845176</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-45.90728634778437,170.56186051115884</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-45.907512612673926,170.56100678810813</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-45.907826204023586,170.5601824713202</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>-45.90818396127301,170.55933439616885</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-45.90836532940878,170.5584346895787</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-45.90830565749401,170.5575288683558</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>-45.90818654773173,170.5566129156902</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>-45.90795617606317,170.5557550110746</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>-45.90702224619712,170.5636171769239</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>-45.90713212644974,170.56273305238787</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-45.90727041674463,170.56185634960207</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-45.90747756435156,170.56099763301955</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-45.907813115149516,170.5601797612026</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>-45.90820487501201,170.55933643056713</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>-45.908438709974675,170.55843774789292</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>-45.908428268782416,170.5575312489806</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>-45.90825212847823,170.55659982520828</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>-45.90801740401748,170.55573033313692</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L475"/>
+  <dimension ref="A1:L481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20360,6 +20360,258 @@
       <c r="L475" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>290.05</v>
+      </c>
+      <c r="C476" t="n">
+        <v>288.49</v>
+      </c>
+      <c r="D476" t="n">
+        <v>290.46</v>
+      </c>
+      <c r="E476" t="n">
+        <v>298.88</v>
+      </c>
+      <c r="F476" t="n">
+        <v>321.76</v>
+      </c>
+      <c r="G476" t="n">
+        <v>357.68</v>
+      </c>
+      <c r="H476" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="I476" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="J476" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="K476" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>289.23</v>
+      </c>
+      <c r="C477" t="n">
+        <v>287.45</v>
+      </c>
+      <c r="D477" t="n">
+        <v>290.03</v>
+      </c>
+      <c r="E477" t="n">
+        <v>298.23</v>
+      </c>
+      <c r="F477" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="G477" t="n">
+        <v>354.77</v>
+      </c>
+      <c r="H477" t="n">
+        <v>382.49</v>
+      </c>
+      <c r="I477" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="J477" t="n">
+        <v>353.49</v>
+      </c>
+      <c r="K477" t="n">
+        <v>343.79</v>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>288.8</v>
+      </c>
+      <c r="C478" t="n">
+        <v>288.14</v>
+      </c>
+      <c r="D478" t="n">
+        <v>289.96</v>
+      </c>
+      <c r="E478" t="n">
+        <v>298.55</v>
+      </c>
+      <c r="F478" t="n">
+        <v>318.71</v>
+      </c>
+      <c r="G478" t="n">
+        <v>354.77</v>
+      </c>
+      <c r="H478" t="n">
+        <v>385.91</v>
+      </c>
+      <c r="I478" t="n">
+        <v>383.25</v>
+      </c>
+      <c r="J478" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="K478" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>287.6</v>
+      </c>
+      <c r="C479" t="n">
+        <v>287</v>
+      </c>
+      <c r="D479" t="n">
+        <v>288.99</v>
+      </c>
+      <c r="E479" t="n">
+        <v>298</v>
+      </c>
+      <c r="F479" t="n">
+        <v>317.52</v>
+      </c>
+      <c r="G479" t="n">
+        <v>352.94</v>
+      </c>
+      <c r="H479" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="I479" t="n">
+        <v>383.95</v>
+      </c>
+      <c r="J479" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="K479" t="n">
+        <v>340.88</v>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>288.36</v>
+      </c>
+      <c r="C480" t="n">
+        <v>288.29</v>
+      </c>
+      <c r="D480" t="n">
+        <v>290.1</v>
+      </c>
+      <c r="E480" t="n">
+        <v>299.36</v>
+      </c>
+      <c r="F480" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="G480" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="H480" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="I480" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="J480" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="K480" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>288.34</v>
+      </c>
+      <c r="C481" t="n">
+        <v>288.77</v>
+      </c>
+      <c r="D481" t="n">
+        <v>290.99</v>
+      </c>
+      <c r="E481" t="n">
+        <v>300.46</v>
+      </c>
+      <c r="F481" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="G481" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="H481" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="I481" t="n">
+        <v>391.54</v>
+      </c>
+      <c r="J481" t="n">
+        <v>353.88</v>
+      </c>
+      <c r="K481" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20374,7 +20626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B544"/>
+  <dimension ref="A1:B550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25817,6 +26069,66 @@
       </c>
       <c r="B544" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -25985,28 +26297,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3281899249959167</v>
+        <v>-0.3096724666233396</v>
       </c>
       <c r="J2" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06775524627481266</v>
+        <v>0.06171962627062366</v>
       </c>
       <c r="M2" t="n">
-        <v>7.418860958959292</v>
+        <v>7.437047920681192</v>
       </c>
       <c r="N2" t="n">
-        <v>82.92931276399923</v>
+        <v>82.64329025222425</v>
       </c>
       <c r="O2" t="n">
-        <v>9.106553286727049</v>
+        <v>9.090835509029093</v>
       </c>
       <c r="P2" t="n">
-        <v>289.6211659898114</v>
+        <v>289.4223016955429</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26063,28 +26375,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4001341959695069</v>
+        <v>-0.3745098844574922</v>
       </c>
       <c r="J3" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K3" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08051919329369484</v>
+        <v>0.07200945317843099</v>
       </c>
       <c r="M3" t="n">
-        <v>8.342139366223661</v>
+        <v>8.37037371652735</v>
       </c>
       <c r="N3" t="n">
-        <v>102.3116637296743</v>
+        <v>102.4645592414036</v>
       </c>
       <c r="O3" t="n">
-        <v>10.1149228237132</v>
+        <v>10.12247792002549</v>
       </c>
       <c r="P3" t="n">
-        <v>287.8158170613873</v>
+        <v>287.5406038038683</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26141,28 +26453,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5126413273849807</v>
+        <v>-0.4869051308106499</v>
       </c>
       <c r="J4" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K4" t="n">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1099707315297406</v>
+        <v>0.101500229933996</v>
       </c>
       <c r="M4" t="n">
-        <v>8.599994590402783</v>
+        <v>8.632607306583758</v>
       </c>
       <c r="N4" t="n">
-        <v>118.9969049908</v>
+        <v>118.955894087861</v>
       </c>
       <c r="O4" t="n">
-        <v>10.90857025419922</v>
+        <v>10.90669033611302</v>
       </c>
       <c r="P4" t="n">
-        <v>292.8241674523326</v>
+        <v>292.54813678563</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26219,28 +26531,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4758262007235368</v>
+        <v>-0.4516849678192212</v>
       </c>
       <c r="J5" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K5" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1048222737963092</v>
+        <v>0.09664083110778221</v>
       </c>
       <c r="M5" t="n">
-        <v>8.119181226469134</v>
+        <v>8.145214898240889</v>
       </c>
       <c r="N5" t="n">
-        <v>108.1688235260911</v>
+        <v>108.0953118417805</v>
       </c>
       <c r="O5" t="n">
-        <v>10.40042419933394</v>
+        <v>10.3968895272471</v>
       </c>
       <c r="P5" t="n">
-        <v>301.3385798730137</v>
+        <v>301.079829120213</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26297,28 +26609,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2865990811456606</v>
+        <v>-0.2571718918445582</v>
       </c>
       <c r="J6" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K6" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03266418620646483</v>
+        <v>0.02676893271028424</v>
       </c>
       <c r="M6" t="n">
-        <v>9.173492743984104</v>
+        <v>9.218424765977668</v>
       </c>
       <c r="N6" t="n">
-        <v>136.0832654824488</v>
+        <v>136.2911608483808</v>
       </c>
       <c r="O6" t="n">
-        <v>11.66547322153923</v>
+        <v>11.67438053381766</v>
       </c>
       <c r="P6" t="n">
-        <v>314.4392768770994</v>
+        <v>314.1239052683535</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26375,28 +26687,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07527870824388562</v>
+        <v>0.1189927707009309</v>
       </c>
       <c r="J7" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K7" t="n">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001179574511618209</v>
+        <v>0.002971712257225922</v>
       </c>
       <c r="M7" t="n">
-        <v>12.75303012857044</v>
+        <v>12.83907896056024</v>
       </c>
       <c r="N7" t="n">
-        <v>266.5139776220969</v>
+        <v>267.3238996707527</v>
       </c>
       <c r="O7" t="n">
-        <v>16.32525582103071</v>
+        <v>16.3500428033309</v>
       </c>
       <c r="P7" t="n">
-        <v>334.2662310214204</v>
+        <v>333.7949364951759</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26453,28 +26765,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2298257761348697</v>
+        <v>0.2909371404325508</v>
       </c>
       <c r="J8" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K8" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007560029992639272</v>
+        <v>0.01211577482988491</v>
       </c>
       <c r="M8" t="n">
-        <v>16.0619176882555</v>
+        <v>16.17897082648247</v>
       </c>
       <c r="N8" t="n">
-        <v>383.6216157362432</v>
+        <v>386.8655542270557</v>
       </c>
       <c r="O8" t="n">
-        <v>19.58626089217243</v>
+        <v>19.66889814471201</v>
       </c>
       <c r="P8" t="n">
-        <v>353.0331719987889</v>
+        <v>352.3721550465394</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26531,28 +26843,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4063975197933926</v>
+        <v>0.463029606185761</v>
       </c>
       <c r="J9" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K9" t="n">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01946780251844793</v>
+        <v>0.02537800015602099</v>
       </c>
       <c r="M9" t="n">
-        <v>17.38889264427404</v>
+        <v>17.4785549798429</v>
       </c>
       <c r="N9" t="n">
-        <v>464.4490394111053</v>
+        <v>465.7473883437534</v>
       </c>
       <c r="O9" t="n">
-        <v>21.5510797736704</v>
+        <v>21.58118134726997</v>
       </c>
       <c r="P9" t="n">
-        <v>349.8308990639987</v>
+        <v>349.2222958108472</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26609,28 +26921,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5574291563332879</v>
+        <v>0.615102275455896</v>
       </c>
       <c r="J10" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K10" t="n">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02637493101740984</v>
+        <v>0.03237867797239136</v>
       </c>
       <c r="M10" t="n">
-        <v>19.9729290542022</v>
+        <v>19.9810425205289</v>
       </c>
       <c r="N10" t="n">
-        <v>636.9065507220449</v>
+        <v>636.1335229445995</v>
       </c>
       <c r="O10" t="n">
-        <v>25.23700756274493</v>
+        <v>25.22168755148234</v>
       </c>
       <c r="P10" t="n">
-        <v>314.2332676538847</v>
+        <v>313.6119288557351</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26687,28 +26999,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3392654604373088</v>
+        <v>0.4461362218436443</v>
       </c>
       <c r="J11" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K11" t="n">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00669125736496512</v>
+        <v>0.01150952297193719</v>
       </c>
       <c r="M11" t="n">
-        <v>24.81311986280667</v>
+        <v>25.01895637611774</v>
       </c>
       <c r="N11" t="n">
-        <v>953.6714389476291</v>
+        <v>966.5845830429782</v>
       </c>
       <c r="O11" t="n">
-        <v>30.88157118651234</v>
+        <v>31.08994343904437</v>
       </c>
       <c r="P11" t="n">
-        <v>287.8233413892212</v>
+        <v>286.6737413796145</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -26750,7 +27062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L475"/>
+  <dimension ref="A1:L481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56127,6 +56439,378 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>-45.90701534276102,170.56361537343977</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>-45.90712637358023,170.56273154954494</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>-45.90726864662909,170.561855887207</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-45.90746800571806,170.56099513617906</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>-45.907794149638015,170.56017583429949</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>-45.90819392447057,170.55933536534556</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>-45.90844671349224,170.55843808145934</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>-45.90846991883805,170.55753205765936</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>-45.90825604906625,170.55659904262404</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>-45.90800969639703,170.55573343969797</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>-45.90700808530253,170.56361347746972</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>-45.90711716898899,170.56272914499678</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>-45.9072648408807,170.56185489305773</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-45.907462252836766,170.56099363345137</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>-45.90777269100746,170.5601713911867</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>-45.9081678047364,170.5593328245315</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>-45.908448242253996,170.55843814517425</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>-45.90846964896726,170.55753205241953</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>-45.90822771390717,170.55660469857102</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>-45.90798224341093,170.55574450463283</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>-45.90700427956209,170.56361248324168</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>-45.907123275881276,170.5627307403219</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>-45.907264221340256,170.56185473121948</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-45.907465085024484,170.56099437325574</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>-45.907766992449936,170.56017021127346</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>-45.9081678047364,170.5593328245315</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>-45.90847899734385,170.5584394269692</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>-45.90848629099806,170.55753237554165</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>-45.908218625271125,170.55660651274133</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>-45.90797756687686,170.5557463895102</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>-45.90699365889104,170.56360970865254</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>-45.90711318623315,170.56272810456755</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>-45.907255636279864,170.56185248860416</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-45.907460217201844,170.56099310171703</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>-45.90775639669451,170.56016801737286</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>-45.90815137892412,170.55933122670095</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>-45.908472162879455,170.5584391421258</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-45.90849258798269,170.5575324978041</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>-45.90821220976332,170.55660779333175</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>-45.90795704208804,170.55575466202356</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>-45.907000385316046,170.56361146589222</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>-45.90712460346653,170.56273108713177</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-45.90726546042114,170.56185505489597</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-45.90747225399961,170.56099624588586</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-45.90776734860978,170.56017028501805</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>-45.90816277825833,170.5593323355778</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>-45.908487090788526,170.55843976428375</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-45.90851687635187,170.55753296938775</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>-45.90822129839939,170.5566059791619</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>-45.90794621677716,170.55575902516094</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>-45.90700020830486,170.56361141964905</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>-45.9071288517394,170.5627321969234</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>-45.90727333743527,170.56185711255398</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-45.90748198964483,170.5609987889645</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>-45.90777669780571,170.56017222081334</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>-45.90816277825833,170.5593323355778</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-45.908487090788526,170.55843976428375</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-45.90856086528693,170.55753382347805</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>-45.90823118897389,170.5566040049175</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>-45.90793383262124,170.55576401658791</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L481"/>
+  <dimension ref="A1:L485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20610,6 +20610,174 @@
         <v>338.2</v>
       </c>
       <c r="L481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>285.28</v>
+      </c>
+      <c r="C482" t="n">
+        <v>288.77</v>
+      </c>
+      <c r="D482" t="n">
+        <v>289.03</v>
+      </c>
+      <c r="E482" t="n">
+        <v>297.58</v>
+      </c>
+      <c r="F482" t="n">
+        <v>316.09</v>
+      </c>
+      <c r="G482" t="n">
+        <v>347.33</v>
+      </c>
+      <c r="H482" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="I482" t="n">
+        <v>391.54</v>
+      </c>
+      <c r="J482" t="n">
+        <v>353.88</v>
+      </c>
+      <c r="K482" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>285.28</v>
+      </c>
+      <c r="C483" t="n">
+        <v>288.77</v>
+      </c>
+      <c r="D483" t="n">
+        <v>288.22</v>
+      </c>
+      <c r="E483" t="n">
+        <v>296.49</v>
+      </c>
+      <c r="F483" t="n">
+        <v>314.07</v>
+      </c>
+      <c r="G483" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="H483" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="I483" t="n">
+        <v>385.37</v>
+      </c>
+      <c r="J483" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="K483" t="n">
+        <v>336.37</v>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>285.24</v>
+      </c>
+      <c r="C484" t="n">
+        <v>288.52</v>
+      </c>
+      <c r="D484" t="n">
+        <v>288.23</v>
+      </c>
+      <c r="E484" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="F484" t="n">
+        <v>311.03</v>
+      </c>
+      <c r="G484" t="n">
+        <v>338.69</v>
+      </c>
+      <c r="H484" t="n">
+        <v>387.34</v>
+      </c>
+      <c r="I484" t="n">
+        <v>386</v>
+      </c>
+      <c r="J484" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="K484" t="n">
+        <v>322.18</v>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>284.31</v>
+      </c>
+      <c r="C485" t="n">
+        <v>287.47</v>
+      </c>
+      <c r="D485" t="n">
+        <v>287.78</v>
+      </c>
+      <c r="E485" t="n">
+        <v>294.79</v>
+      </c>
+      <c r="F485" t="n">
+        <v>309.83</v>
+      </c>
+      <c r="G485" t="n">
+        <v>337.04</v>
+      </c>
+      <c r="H485" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="I485" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="J485" t="n">
+        <v>345.18</v>
+      </c>
+      <c r="K485" t="n">
+        <v>310.65</v>
+      </c>
+      <c r="L485" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20626,7 +20794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B550"/>
+  <dimension ref="A1:B554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26129,6 +26297,46 @@
       </c>
       <c r="B550" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -26297,28 +26505,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3096724666233396</v>
+        <v>-0.3036401488072882</v>
       </c>
       <c r="J2" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K2" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06171962627062366</v>
+        <v>0.06033434661290504</v>
       </c>
       <c r="M2" t="n">
-        <v>7.437047920681192</v>
+        <v>7.410899721341495</v>
       </c>
       <c r="N2" t="n">
-        <v>82.64329025222425</v>
+        <v>82.081038711841</v>
       </c>
       <c r="O2" t="n">
-        <v>9.090835509029093</v>
+        <v>9.059858647453668</v>
       </c>
       <c r="P2" t="n">
-        <v>289.4223016955429</v>
+        <v>289.3571984529688</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26375,28 +26583,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3745098844574922</v>
+        <v>-0.3576981096748998</v>
       </c>
       <c r="J3" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K3" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07200945317843099</v>
+        <v>0.06655737732908884</v>
       </c>
       <c r="M3" t="n">
-        <v>8.37037371652735</v>
+        <v>8.388484536717733</v>
       </c>
       <c r="N3" t="n">
-        <v>102.4645592414036</v>
+        <v>102.574741446983</v>
       </c>
       <c r="O3" t="n">
-        <v>10.12247792002549</v>
+        <v>10.12791890997272</v>
       </c>
       <c r="P3" t="n">
-        <v>287.5406038038683</v>
+        <v>287.3591611992277</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26453,28 +26661,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4869051308106499</v>
+        <v>-0.4733013025128675</v>
       </c>
       <c r="J4" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K4" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L4" t="n">
-        <v>0.101500229933996</v>
+        <v>0.09744544214651663</v>
       </c>
       <c r="M4" t="n">
-        <v>8.632607306583758</v>
+        <v>8.636667164998167</v>
       </c>
       <c r="N4" t="n">
-        <v>118.955894087861</v>
+        <v>118.5998141624944</v>
       </c>
       <c r="O4" t="n">
-        <v>10.90669033611302</v>
+        <v>10.89035417984624</v>
       </c>
       <c r="P4" t="n">
-        <v>292.54813678563</v>
+        <v>292.4015231643113</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26531,28 +26739,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4516849678192212</v>
+        <v>-0.4407332102863902</v>
       </c>
       <c r="J5" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K5" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09664083110778221</v>
+        <v>0.09352433731121601</v>
       </c>
       <c r="M5" t="n">
-        <v>8.145214898240889</v>
+        <v>8.134796603720002</v>
       </c>
       <c r="N5" t="n">
-        <v>108.0953118417805</v>
+        <v>107.6174980776656</v>
       </c>
       <c r="O5" t="n">
-        <v>10.3968895272471</v>
+        <v>10.37388538965346</v>
       </c>
       <c r="P5" t="n">
-        <v>301.079829120213</v>
+        <v>300.9618897713752</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26609,28 +26817,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2571718918445582</v>
+        <v>-0.2486556099503847</v>
       </c>
       <c r="J6" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K6" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02676893271028424</v>
+        <v>0.02542706920501836</v>
       </c>
       <c r="M6" t="n">
-        <v>9.218424765977668</v>
+        <v>9.187972120706455</v>
       </c>
       <c r="N6" t="n">
-        <v>136.2911608483808</v>
+        <v>135.4610356708373</v>
       </c>
       <c r="O6" t="n">
-        <v>11.67438053381766</v>
+        <v>11.63877294523943</v>
       </c>
       <c r="P6" t="n">
-        <v>314.1239052683535</v>
+        <v>314.0322074634703</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26687,28 +26895,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1189927707009309</v>
+        <v>0.1262650793884448</v>
       </c>
       <c r="J7" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K7" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002971712257225922</v>
+        <v>0.00339712188072927</v>
       </c>
       <c r="M7" t="n">
-        <v>12.83907896056024</v>
+        <v>12.77417915514972</v>
       </c>
       <c r="N7" t="n">
-        <v>267.3238996707527</v>
+        <v>265.4206878591232</v>
       </c>
       <c r="O7" t="n">
-        <v>16.3500428033309</v>
+        <v>16.2917367968895</v>
       </c>
       <c r="P7" t="n">
-        <v>333.7949364951759</v>
+        <v>333.7161805406046</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26765,28 +26973,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2909371404325508</v>
+        <v>0.3317575539945779</v>
       </c>
       <c r="J8" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K8" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01211577482988491</v>
+        <v>0.01573336437288608</v>
       </c>
       <c r="M8" t="n">
-        <v>16.17897082648247</v>
+        <v>16.26038650950531</v>
       </c>
       <c r="N8" t="n">
-        <v>386.8655542270557</v>
+        <v>389.2249905883487</v>
       </c>
       <c r="O8" t="n">
-        <v>19.66889814471201</v>
+        <v>19.72878583664866</v>
       </c>
       <c r="P8" t="n">
-        <v>352.3721550465394</v>
+        <v>351.9285164904487</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26843,28 +27051,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.463029606185761</v>
+        <v>0.5013325564793724</v>
       </c>
       <c r="J9" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K9" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02537800015602099</v>
+        <v>0.0297899284307499</v>
       </c>
       <c r="M9" t="n">
-        <v>17.4785549798429</v>
+        <v>17.54344080995666</v>
       </c>
       <c r="N9" t="n">
-        <v>465.7473883437534</v>
+        <v>466.9292205394942</v>
       </c>
       <c r="O9" t="n">
-        <v>21.58118134726997</v>
+        <v>21.60854508150639</v>
       </c>
       <c r="P9" t="n">
-        <v>349.2222958108472</v>
+        <v>348.8087427933439</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26921,28 +27129,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.615102275455896</v>
+        <v>0.645241476970046</v>
       </c>
       <c r="J10" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K10" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03237867797239136</v>
+        <v>0.0359220213624093</v>
       </c>
       <c r="M10" t="n">
-        <v>19.9810425205289</v>
+        <v>19.94888454910701</v>
       </c>
       <c r="N10" t="n">
-        <v>636.1335229445995</v>
+        <v>633.9914368622988</v>
       </c>
       <c r="O10" t="n">
-        <v>25.22168755148234</v>
+        <v>25.1791865806324</v>
       </c>
       <c r="P10" t="n">
-        <v>313.6119288557351</v>
+        <v>313.2856672748011</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26999,28 +27207,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4461362218436443</v>
+        <v>0.4898953295366738</v>
       </c>
       <c r="J11" t="n">
+        <v>484</v>
+      </c>
+      <c r="K11" t="n">
         <v>480</v>
       </c>
-      <c r="K11" t="n">
-        <v>476</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01150952297193719</v>
+        <v>0.01396770016528426</v>
       </c>
       <c r="M11" t="n">
-        <v>25.01895637611774</v>
+        <v>25.02279026508137</v>
       </c>
       <c r="N11" t="n">
-        <v>966.5845830429782</v>
+        <v>966.0515685978055</v>
       </c>
       <c r="O11" t="n">
-        <v>31.08994343904437</v>
+        <v>31.08137012098735</v>
       </c>
       <c r="P11" t="n">
-        <v>286.6737413796145</v>
+        <v>286.2007890765478</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -27062,7 +27270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L481"/>
+  <dimension ref="A1:L485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56811,6 +57019,254 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>-45.90697312559352,170.5636043444496</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>-45.9071288517394,170.5627321969234</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>-45.90725599030298,170.56185258108314</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-45.90745649995546,170.56099213072395</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>-45.90774366397995,170.5601653810059</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>-45.90810102438456,170.55932632843815</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-45.908487090788526,170.55843976428375</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-45.90856086528693,170.55753382347805</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>-45.90823118897389,170.5566040049175</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>-45.90793383262124,170.55576401658791</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>-45.90697312559352,170.5636043444496</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>-45.9071288517394,170.5627321969234</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>-45.90724882133498,170.5618507083842</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-45.90744685281598,170.56098961076637</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>-45.90772567790753,170.56016165690895</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-45.90806772396691,170.55932308912742</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-45.908487090788526,170.55843976428375</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-45.90850536186575,170.5575327458222</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-45.90819884412193,170.55661046122742</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>-45.90791798436535,170.55577040421485</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>-45.906972771571155,170.56360425196337</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>-45.907126639097285,170.5627316189069</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>-45.90724890984075,170.56185073150397</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-45.90743764820579,170.56098720640387</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>-45.9076986097587,170.5601560523315</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>-45.90802347300727,170.55931878460328</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-45.90849185692816,170.55843996292458</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-45.90851102915189,170.55753285585834</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>-45.90818538937614,170.55661314690764</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>-45.90779509541435,170.55581993437315</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>-45.90696454055095,170.56360210165894</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>-45.90711734600037,170.5627291912381</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>-45.90724492708075,170.56184969111584</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-45.90743180681853,170.56098568055884</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>-45.90768792496302,170.56015383999969</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>-45.9080086628483,170.55931734394227</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-45.90846631761384,170.5584388985098</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-45.908480803625764,170.55753226899867</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>-45.90815366825316,170.55661947870433</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>-45.907695242708144,170.55586017963958</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
